--- a/excepciones_spoofing.xlsx
+++ b/excepciones_spoofing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Python\ProyectosIA\fishingscanner\dist\phishing_scanner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Python\ProyectosIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68A3BA6-A2CF-4064-A06C-B4A610F01B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDB7123-F5A8-4907-84F6-4D2A1E790E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>EXCEPCIONES DE DOMINIOS — ESCÁNER ANTIPHISHING</t>
   </si>
@@ -252,9 +252,6 @@
   </si>
   <si>
     <t>agrofresh.com</t>
-  </si>
-  <si>
-    <t>newticsoluciones.es</t>
   </si>
 </sst>
 </file>
@@ -702,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -834,13 +831,13 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -853,74 +850,54 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8">
-        <v>46097</v>
+      <c r="F9" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/excepciones_spoofing.xlsx
+++ b/excepciones_spoofing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Python\ProyectosIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Python\ProyectosIA\fishingscanner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDB7123-F5A8-4907-84F6-4D2A1E790E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E65137D-CBA8-48EF-BB28-730DEEC348D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excepciones Spoofing" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
   <si>
     <t>EXCEPCIONES DE DOMINIOS — ESCÁNER ANTIPHISHING</t>
   </si>
@@ -252,13 +252,46 @@
   </si>
   <si>
     <t>agrofresh.com</t>
+  </si>
+  <si>
+    <t>telefonica.com</t>
+  </si>
+  <si>
+    <t>newticsoluciones.es</t>
+  </si>
+  <si>
+    <t>dibal.com</t>
+  </si>
+  <si>
+    <t>exchangelabs.com</t>
+  </si>
+  <si>
+    <t>Cosas de Dibal</t>
+  </si>
+  <si>
+    <t>localhost.localdomain</t>
+  </si>
+  <si>
+    <t>jeronimo-martins.com</t>
+  </si>
+  <si>
+    <t>driscolls.eu</t>
+  </si>
+  <si>
+    <t>masorange.es</t>
+  </si>
+  <si>
+    <t>calidad.telefonica.es</t>
+  </si>
+  <si>
+    <t>Newsletter automática vía Amazon SES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +331,11 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -370,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -388,6 +426,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -699,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -710,24 +751,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -800,7 +841,7 @@
         <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -811,33 +852,33 @@
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="8">
-        <v>46097</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -850,54 +891,214 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>13</v>
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="8">
+        <v>46099</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="8">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4" t="s">
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
